--- a/BESS_Dashboard.xlsx
+++ b/BESS_Dashboard.xlsx
@@ -18,12 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="€#,##0"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="€0.00"/>
-  </numFmts>
-  <fonts count="14">
+  <numFmts count="0"/>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,7 +59,7 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="003C3C3C"/>
       <sz val="8"/>
     </font>
     <font>
@@ -75,7 +71,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="001A3A24"/>
       <sz val="9"/>
     </font>
     <font>
@@ -85,27 +81,21 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00842019"/>
+      <color rgb="007A2020"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00375623"/>
+      <color rgb="001A3A24"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="007F6000"/>
+      <color rgb="008A6820"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -114,47 +104,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="001A3A24"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="002D6840"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00F5F2EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E8B57"/>
+        <fgColor rgb="00D4E8D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00375623"/>
+        <fgColor rgb="00F5E8C8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F5D5D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -212,21 +187,12 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -236,157 +202,76 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -785,7 +670,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PAISTINKULMA BESS  —  PERFORMANCE &amp; INVESTMENT SUMMARY</t>
+          <t>BESS  —  PERFORMANCE &amp; INVESTMENT SUMMARY</t>
         </is>
       </c>
     </row>
@@ -793,7 +678,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>30 MW / 36 MWh Battery Energy Storage  ·  Lempäälä, Finland  ·  Analysis period: Full Year 2025  ·  Data: ENTSO-E (spot prices) + Fingrid Open Data (reserve markets)</t>
+          <t>30 MW / 36 MWh Battery Energy Storage  ·  Finland  ·  Analysis period: Full Year 2025  ·  Data: ENTSO-E (spot prices) + Fingrid Open Data (reserve markets)</t>
         </is>
       </c>
     </row>
@@ -819,7 +704,7 @@
           <t>Model Revenue  Y1</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Operational Revenue  Y1</t>
         </is>
@@ -829,12 +714,12 @@
           <t>Revenue / MW / Month</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>Project NPV</t>
         </is>
@@ -846,64 +731,64 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>€5.91 M</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>€4.73 M</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>€13,126</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>32.5%</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>€26.5 M</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>3.1 yrs</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Perfect foresight upper bound</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>After −20% operational haircut</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Operational estimate</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Unlevered, 20-year horizon</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>At 8% WACC</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr">
         <is>
           <t>Undiscounted</t>
         </is>
@@ -924,490 +809,648 @@
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>% of Year</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Revenue (€)</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>% of Rev.</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Avg €/hr</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>Revenue (€ M)</t>
         </is>
       </c>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>vs. Spot Naive</t>
         </is>
       </c>
-      <c r="M14" s="13" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>vs. FCR-D Naive</t>
         </is>
       </c>
-      <c r="N14" s="13" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Dominant Market</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>FCR-N  (Frequency Reserve – Normal)</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
-        <v>4617</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>0.5270547945205479</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>2346890.1</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.3986313717505278</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>508.3149447693307</v>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>4 617</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>€ 2 346 890</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>€ 508</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="K15" s="18" t="n">
-        <v>0.81360982608375</v>
-      </c>
-      <c r="L15" s="19" t="n">
-        <v>-0.14613937391625</v>
-      </c>
-      <c r="M15" s="20" t="n">
-        <v>0.5322644260837499</v>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>€ 0.81 M</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>-€ 0.15 M</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.53 M</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="inlineStr">
         <is>
           <t>FCR-D Down</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>FCR-D Up  (Frequency Reserve – Disturbance)</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
-        <v>2435</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>0.2779680365296804</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>2005126.8</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>0.340581114905102</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>823.4606981519507</v>
-      </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>2 435</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>€ 2 005 127</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>€ 823</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="K16" s="23" t="n">
-        <v>0.6593748</v>
-      </c>
-      <c r="L16" s="24" t="n">
-        <v>-0.1070937</v>
-      </c>
-      <c r="M16" s="25" t="n">
-        <v>0.5412921000000001</v>
-      </c>
-      <c r="N16" s="26" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>€ 0.66 M</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>-€ 0.11 M</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="inlineStr">
+        <is>
+          <t>+€ 0.54 M</t>
+        </is>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>FCR-N</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>FCR-D Down  (Frequency Reserve – Absorption)</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
-        <v>1560</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>0.1780821917808219</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>1543784.4</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>0.2622197320015391</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <v>989.6053846153845</v>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>1 560</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>€ 1 543 784</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>€ 990</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="K17" s="18" t="n">
-        <v>0.6805964236762498</v>
-      </c>
-      <c r="L17" s="19" t="n">
-        <v>-0.2501499763237501</v>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>0.5037266236762499</v>
-      </c>
-      <c r="N17" s="21" t="inlineStr">
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>€ 0.68 M</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>-€ 0.25 M</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.50 M</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>FCR-N</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>mFRR Up  (Manual Restoration – Up)</t>
         </is>
       </c>
-      <c r="C18" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0.001255707762557078</v>
-      </c>
-      <c r="E18" s="30" t="n">
-        <v>6818.11944515604</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0.001158092706250497</v>
-      </c>
-      <c r="G18" s="30" t="n">
-        <v>619.8290404687309</v>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>€ 6 818</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>€ 620</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="K18" s="23" t="n">
-        <v>0.4842586339335444</v>
-      </c>
-      <c r="L18" s="24" t="n">
-        <v>-0.3897325660664556</v>
-      </c>
-      <c r="M18" s="25" t="n">
-        <v>0.2019706339335444</v>
-      </c>
-      <c r="N18" s="26" t="inlineStr">
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>€ 0.48 M</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>-€ 0.39 M</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="inlineStr">
+        <is>
+          <t>+€ 0.20 M</t>
+        </is>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>FCR-N</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Spot Arbitrage  (Day-ahead discharge)</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="33" t="n">
-        <v>0.0005707762557077625</v>
-      </c>
-      <c r="E19" s="34" t="n">
-        <v>2728.44523687492</v>
-      </c>
-      <c r="F19" s="33" t="n">
-        <v>0.0004634404770473245</v>
-      </c>
-      <c r="G19" s="34" t="n">
-        <v>545.6890473749841</v>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>€ 2 728</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>€ 546</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="K19" s="18" t="n">
-        <v>0.4430500411973684</v>
-      </c>
-      <c r="L19" s="20" t="n">
-        <v>0.2039695411973684</v>
-      </c>
-      <c r="M19" s="20" t="n">
-        <v>0.06728444119736843</v>
-      </c>
-      <c r="N19" s="21" t="inlineStr">
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>€ 0.44 M</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.20 M</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.07 M</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="inlineStr">
         <is>
           <t>FCR-D Up</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>mFRR Down  (Manual Restoration – Down)</t>
         </is>
       </c>
-      <c r="C20" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0.0007990867579908676</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>627.567</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0.000106595487396433</v>
-      </c>
-      <c r="G20" s="30" t="n">
-        <v>89.65242857142857</v>
-      </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>€ 628</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>€ 90</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="K20" s="23" t="n">
-        <v>0.5363860603134568</v>
-      </c>
-      <c r="L20" s="25" t="n">
-        <v>0.2355028603134568</v>
-      </c>
-      <c r="M20" s="25" t="n">
-        <v>0.06665206031345683</v>
-      </c>
-      <c r="N20" s="26" t="inlineStr">
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>€ 0.54 M</t>
+        </is>
+      </c>
+      <c r="L20" s="19" t="inlineStr">
+        <is>
+          <t>+€ 0.24 M</t>
+        </is>
+      </c>
+      <c r="M20" s="19" t="inlineStr">
+        <is>
+          <t>+€ 0.07 M</t>
+        </is>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>FCR-D Up</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Grid Charging  (Off-peak recharge)</t>
         </is>
       </c>
-      <c r="C21" s="36" t="n">
-        <v>125</v>
-      </c>
-      <c r="D21" s="37" t="n">
-        <v>0.01426940639269406</v>
-      </c>
-      <c r="E21" s="38" t="n">
-        <v>-18606.13183491586</v>
-      </c>
-      <c r="F21" s="37" t="n">
-        <v>-0.003160347327863232</v>
-      </c>
-      <c r="G21" s="38" t="n">
-        <v>-148.8490546793269</v>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>-€ 18 606</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>-€ 149</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="K21" s="18" t="n">
-        <v>0.3884609737894737</v>
-      </c>
-      <c r="L21" s="20" t="n">
-        <v>0.2088338737894737</v>
-      </c>
-      <c r="M21" s="20" t="n">
-        <v>0.0405086737894737</v>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>€ 0.39 M</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.21 M</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.04 M</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
         <is>
           <t>FCR-D Up</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C22" s="40" t="n">
-        <v>8760</v>
-      </c>
-      <c r="D22" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="42" t="n">
-        <v>5887369.299847116</v>
-      </c>
-      <c r="F22" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="42" t="n">
-        <v>672.0741209871137</v>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>8 760</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>€ 5 887 369</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>€ 672</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="K22" s="23" t="n">
-        <v>0.768024</v>
-      </c>
-      <c r="L22" s="24" t="n">
-        <v>-0.3457821000000001</v>
-      </c>
-      <c r="M22" s="25" t="n">
-        <v>0.3642513000000001</v>
-      </c>
-      <c r="N22" s="26" t="inlineStr">
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>€ 0.77 M</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>-€ 0.35 M</t>
+        </is>
+      </c>
+      <c r="M22" s="19" t="inlineStr">
+        <is>
+          <t>+€ 0.36 M</t>
+        </is>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>FCR-D Down</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="K23" s="18" t="n">
-        <v>0.54721875009375</v>
-      </c>
-      <c r="L23" s="19" t="n">
-        <v>-0.16442474990625</v>
-      </c>
-      <c r="M23" s="20" t="n">
-        <v>0.32745855009375</v>
-      </c>
-      <c r="N23" s="21" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>€ 0.55 M</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>-€ 0.16 M</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.33 M</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
         <is>
           <t>FCR-D Down</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="K24" s="23" t="n">
-        <v>0.2715381</v>
-      </c>
-      <c r="L24" s="24" t="n">
-        <v>-0.6646922249999999</v>
-      </c>
-      <c r="M24" s="25" t="n">
-        <v>0.1064655</v>
-      </c>
-      <c r="N24" s="26" t="inlineStr">
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>€ 0.27 M</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>-€ 0.66 M</t>
+        </is>
+      </c>
+      <c r="M24" s="19" t="inlineStr">
+        <is>
+          <t>+€ 0.11 M</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>FCR-N</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="J25" s="14" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
-      <c r="K25" s="18" t="n">
-        <v>0.1982071155</v>
-      </c>
-      <c r="L25" s="19" t="n">
-        <v>-0.6283109594999999</v>
-      </c>
-      <c r="M25" s="20" t="n">
-        <v>0.0602161155</v>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>€ 0.20 M</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>-€ 0.63 M</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>+€ 0.06 M</t>
+        </is>
+      </c>
+      <c r="N25" s="15" t="inlineStr">
         <is>
           <t>FCR-N</t>
         </is>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="K26" s="23" t="n">
-        <v>0.1159669515</v>
-      </c>
-      <c r="L26" s="24" t="n">
-        <v>-0.3632531985</v>
-      </c>
-      <c r="M26" s="25" t="n">
-        <v>0.0614098515</v>
-      </c>
-      <c r="N26" s="26" t="inlineStr">
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>€ 0.12 M</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>-€ 0.36 M</t>
+        </is>
+      </c>
+      <c r="M26" s="19" t="inlineStr">
+        <is>
+          <t>+€ 0.06 M</t>
+        </is>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>FCR-N</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="J27" s="39" t="inlineStr">
+      <c r="J27" s="25" t="inlineStr">
         <is>
           <t>FULL YEAR</t>
         </is>
       </c>
-      <c r="K27" s="43" t="n">
-        <v>5.906691676087592</v>
-      </c>
-      <c r="L27" s="44" t="n">
-        <v>-2.411272573912409</v>
-      </c>
-      <c r="M27" s="44" t="n">
-        <v>2.873500276087593</v>
-      </c>
-      <c r="N27" s="45" t="inlineStr"/>
+      <c r="K27" s="26" t="inlineStr">
+        <is>
+          <t>€ 5.91 M</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="inlineStr">
+        <is>
+          <t>-€ 2.41 M</t>
+        </is>
+      </c>
+      <c r="M27" s="26" t="inlineStr">
+        <is>
+          <t>+€ 2.87 M</t>
+        </is>
+      </c>
+      <c r="N27" s="26" t="inlineStr"/>
     </row>
     <row r="29" ht="16" customHeight="1"/>
     <row r="30" ht="4" customHeight="1"/>
@@ -1424,568 +1467,761 @@
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="L32" s="13" t="inlineStr">
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>Free CF</t>
         </is>
       </c>
-      <c r="M32" s="13" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Cumul. CF</t>
         </is>
       </c>
-      <c r="N32" s="13" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>CAPEX</t>
         </is>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>€12 M</t>
         </is>
       </c>
-      <c r="G33" s="26" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>€400/kW total installed cost</t>
         </is>
       </c>
-      <c r="J33" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="48" t="n">
-        <v>4.725353340870074</v>
-      </c>
-      <c r="L33" s="48" t="n">
-        <v>3.857381259332579</v>
-      </c>
-      <c r="M33" s="49" t="n">
-        <v>-8.142618740667421</v>
-      </c>
-      <c r="N33" s="50" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr"/>
+      <c r="F33" s="12" t="inlineStr"/>
+      <c r="G33" s="12" t="inlineStr"/>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>€ 4.73 M</t>
+        </is>
+      </c>
+      <c r="L33" s="24" t="inlineStr">
+        <is>
+          <t>+€ 3.86 M</t>
+        </is>
+      </c>
+      <c r="M33" s="27" t="inlineStr">
+        <is>
+          <t>-€ 8.14 M</t>
+        </is>
+      </c>
+      <c r="N33" s="28" t="inlineStr">
         <is>
           <t>Payback period</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="B34" s="51" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>OPEX (fixed)</t>
         </is>
       </c>
-      <c r="E34" s="52" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>€180,000 / yr</t>
         </is>
       </c>
-      <c r="G34" s="52" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>1.5% of CAPEX annually</t>
         </is>
       </c>
-      <c r="J34" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="48" t="n">
-        <v>4.769771662274253</v>
-      </c>
-      <c r="L34" s="48" t="n">
-        <v>3.892738243170305</v>
-      </c>
-      <c r="M34" s="49" t="n">
-        <v>-4.249880497497116</v>
-      </c>
-      <c r="N34" s="50" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr"/>
+      <c r="F34" s="17" t="inlineStr"/>
+      <c r="G34" s="17" t="inlineStr"/>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>€ 4.77 M</t>
+        </is>
+      </c>
+      <c r="L34" s="24" t="inlineStr">
+        <is>
+          <t>+€ 3.89 M</t>
+        </is>
+      </c>
+      <c r="M34" s="27" t="inlineStr">
+        <is>
+          <t>-€ 4.25 M</t>
+        </is>
+      </c>
+      <c r="N34" s="28" t="inlineStr">
         <is>
           <t>Payback period</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="B35" s="46" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Revenue Y1</t>
         </is>
       </c>
-      <c r="E35" s="26" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>€4.73 M</t>
         </is>
       </c>
-      <c r="G35" s="26" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>Operational estimate (−20% haircut)</t>
         </is>
       </c>
-      <c r="J35" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="48" t="n">
-        <v>4.81460751589963</v>
-      </c>
-      <c r="L35" s="48" t="n">
-        <v>3.928427582656106</v>
-      </c>
-      <c r="M35" s="49" t="n">
-        <v>-0.3214529148410112</v>
-      </c>
-      <c r="N35" s="50" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="inlineStr"/>
+      <c r="G35" s="12" t="inlineStr"/>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>€ 4.81 M</t>
+        </is>
+      </c>
+      <c r="L35" s="24" t="inlineStr">
+        <is>
+          <t>+€ 3.93 M</t>
+        </is>
+      </c>
+      <c r="M35" s="27" t="inlineStr">
+        <is>
+          <t>-€ 0.32 M</t>
+        </is>
+      </c>
+      <c r="N35" s="28" t="inlineStr">
         <is>
           <t>Payback period</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="B36" s="51" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="E36" s="52" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>3.0% p.a.</t>
         </is>
       </c>
-      <c r="G36" s="52" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>Reserve demand +134% forecast (5 yr)</t>
         </is>
       </c>
-      <c r="J36" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" s="54" t="n">
-        <v>4.859864826549087</v>
-      </c>
-      <c r="L36" s="54" t="n">
-        <v>3.964452401933073</v>
-      </c>
-      <c r="M36" s="55" t="n">
-        <v>3.642999487092063</v>
-      </c>
-      <c r="N36" s="56" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr"/>
+      <c r="F36" s="17" t="inlineStr"/>
+      <c r="G36" s="17" t="inlineStr"/>
+      <c r="J36" s="29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K36" s="29" t="inlineStr">
+        <is>
+          <t>€ 4.86 M</t>
+        </is>
+      </c>
+      <c r="L36" s="29" t="inlineStr">
+        <is>
+          <t>+€ 3.96 M</t>
+        </is>
+      </c>
+      <c r="M36" s="30" t="inlineStr">
+        <is>
+          <t>+€ 3.64 M</t>
+        </is>
+      </c>
+      <c r="N36" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Degradation</t>
         </is>
       </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>2.0% p.a.</t>
         </is>
       </c>
-      <c r="G37" s="26" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>LFP cell capacity loss</t>
         </is>
       </c>
-      <c r="J37" s="57" t="n">
-        <v>5</v>
-      </c>
-      <c r="K37" s="58" t="n">
-        <v>4.905547555918649</v>
-      </c>
-      <c r="L37" s="58" t="n">
-        <v>4.000815854511245</v>
-      </c>
-      <c r="M37" s="59" t="n">
-        <v>7.643815341603309</v>
-      </c>
-      <c r="N37" s="60" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr"/>
+      <c r="F37" s="12" t="inlineStr"/>
+      <c r="G37" s="12" t="inlineStr"/>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>€ 4.91 M</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>+€ 4.00 M</t>
+        </is>
+      </c>
+      <c r="M37" s="19" t="inlineStr">
+        <is>
+          <t>+€ 7.64 M</t>
+        </is>
+      </c>
+      <c r="N37" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="B38" s="51" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Cell replacement</t>
         </is>
       </c>
-      <c r="E38" s="52" t="inlineStr">
-        <is>
-          <t>€3.5 M at year 12</t>
-        </is>
-      </c>
-      <c r="G38" s="52" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>€3.5 M at yr 12</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Cells only; inverters retained</t>
         </is>
       </c>
-      <c r="J38" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K38" s="54" t="n">
-        <v>4.951659702944283</v>
-      </c>
-      <c r="L38" s="54" t="n">
-        <v>4.03752112354365</v>
-      </c>
-      <c r="M38" s="55" t="n">
-        <v>11.68133646514696</v>
-      </c>
-      <c r="N38" s="56" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr"/>
+      <c r="F38" s="17" t="inlineStr"/>
+      <c r="G38" s="17" t="inlineStr"/>
+      <c r="J38" s="29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" s="29" t="inlineStr">
+        <is>
+          <t>€ 4.95 M</t>
+        </is>
+      </c>
+      <c r="L38" s="29" t="inlineStr">
+        <is>
+          <t>+€ 4.04 M</t>
+        </is>
+      </c>
+      <c r="M38" s="30" t="inlineStr">
+        <is>
+          <t>+€ 11.68 M</t>
+        </is>
+      </c>
+      <c r="N38" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="B39" s="46" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Discount rate</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>8.0% WACC</t>
         </is>
       </c>
-      <c r="G39" s="26" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>Infrastructure equity target</t>
         </is>
       </c>
-      <c r="J39" s="57" t="n">
-        <v>7</v>
-      </c>
-      <c r="K39" s="58" t="n">
-        <v>4.998205304151961</v>
-      </c>
-      <c r="L39" s="58" t="n">
-        <v>4.07457142210496</v>
-      </c>
-      <c r="M39" s="59" t="n">
-        <v>15.75590788725192</v>
-      </c>
-      <c r="N39" s="60" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr"/>
+      <c r="F39" s="12" t="inlineStr"/>
+      <c r="G39" s="12" t="inlineStr"/>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>€ 5.00 M</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="inlineStr">
+        <is>
+          <t>+€ 4.07 M</t>
+        </is>
+      </c>
+      <c r="M39" s="19" t="inlineStr">
+        <is>
+          <t>+€ 15.76 M</t>
+        </is>
+      </c>
+      <c r="N39" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="B40" s="51" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Corporation tax</t>
         </is>
       </c>
-      <c r="E40" s="52" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G40" s="52" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="J40" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="K40" s="54" t="n">
-        <v>5.045188434010989</v>
-      </c>
-      <c r="L40" s="54" t="n">
-        <v>4.111969993472748</v>
-      </c>
-      <c r="M40" s="55" t="n">
-        <v>19.86787788072467</v>
-      </c>
-      <c r="N40" s="56" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr"/>
+      <c r="F40" s="17" t="inlineStr"/>
+      <c r="G40" s="17" t="inlineStr"/>
+      <c r="J40" s="29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K40" s="29" t="inlineStr">
+        <is>
+          <t>€ 5.05 M</t>
+        </is>
+      </c>
+      <c r="L40" s="29" t="inlineStr">
+        <is>
+          <t>+€ 4.11 M</t>
+        </is>
+      </c>
+      <c r="M40" s="30" t="inlineStr">
+        <is>
+          <t>+€ 19.87 M</t>
+        </is>
+      </c>
+      <c r="N40" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="B41" s="46" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>10 yr straight-line</t>
         </is>
       </c>
-      <c r="G41" s="26" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>Initial CAPEX basis</t>
         </is>
       </c>
-      <c r="J41" s="57" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" s="58" t="n">
-        <v>5.092613205290693</v>
-      </c>
-      <c r="L41" s="58" t="n">
-        <v>4.149720111411392</v>
-      </c>
-      <c r="M41" s="59" t="n">
-        <v>24.01759799213606</v>
-      </c>
-      <c r="N41" s="60" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr"/>
+      <c r="F41" s="12" t="inlineStr"/>
+      <c r="G41" s="12" t="inlineStr"/>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t>€ 5.09 M</t>
+        </is>
+      </c>
+      <c r="L41" s="17" t="inlineStr">
+        <is>
+          <t>+€ 4.15 M</t>
+        </is>
+      </c>
+      <c r="M41" s="19" t="inlineStr">
+        <is>
+          <t>+€ 24.02 M</t>
+        </is>
+      </c>
+      <c r="N41" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="B42" s="51" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Project life</t>
         </is>
       </c>
-      <c r="E42" s="52" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>20 years</t>
         </is>
       </c>
-      <c r="G42" s="52" t="inlineStr"/>
-      <c r="J42" s="53" t="n">
-        <v>10</v>
-      </c>
-      <c r="K42" s="54" t="n">
-        <v>5.140483769420425</v>
-      </c>
-      <c r="L42" s="54" t="n">
-        <v>4.187825080458659</v>
-      </c>
-      <c r="M42" s="55" t="n">
-        <v>28.20542307259472</v>
-      </c>
-      <c r="N42" s="56" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr"/>
+      <c r="E42" s="17" t="inlineStr"/>
+      <c r="F42" s="17" t="inlineStr"/>
+      <c r="G42" s="17" t="inlineStr"/>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="inlineStr">
+        <is>
+          <t>€ 5.14 M</t>
+        </is>
+      </c>
+      <c r="L42" s="29" t="inlineStr">
+        <is>
+          <t>+€ 4.19 M</t>
+        </is>
+      </c>
+      <c r="M42" s="30" t="inlineStr">
+        <is>
+          <t>+€ 28.21 M</t>
+        </is>
+      </c>
+      <c r="N42" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="J43" s="57" t="n">
-        <v>11</v>
-      </c>
-      <c r="K43" s="58" t="n">
-        <v>5.188804316852977</v>
-      </c>
-      <c r="L43" s="58" t="n">
-        <v>3.986288236214969</v>
-      </c>
-      <c r="M43" s="59" t="n">
-        <v>32.19171130880968</v>
-      </c>
-      <c r="N43" s="60" t="inlineStr">
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>€ 5.19 M</t>
+        </is>
+      </c>
+      <c r="L43" s="17" t="inlineStr">
+        <is>
+          <t>+€ 3.99 M</t>
+        </is>
+      </c>
+      <c r="M43" s="19" t="inlineStr">
+        <is>
+          <t>+€ 32.19 M</t>
+        </is>
+      </c>
+      <c r="N43" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="J44" s="61" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" s="62" t="n">
-        <v>5.237579077431395</v>
-      </c>
-      <c r="L44" s="62" t="n">
-        <v>0.5251129456353905</v>
-      </c>
-      <c r="M44" s="63" t="n">
-        <v>32.71682425444508</v>
-      </c>
-      <c r="N44" s="64" t="inlineStr">
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="inlineStr">
+        <is>
+          <t>€ 5.24 M</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr">
+        <is>
+          <t>+€ 0.53 M</t>
+        </is>
+      </c>
+      <c r="M44" s="33" t="inlineStr">
+        <is>
+          <t>+€ 32.72 M</t>
+        </is>
+      </c>
+      <c r="N44" s="34" t="inlineStr">
         <is>
           <t>Cell replacement</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="J45" s="57" t="n">
-        <v>13</v>
-      </c>
-      <c r="K45" s="58" t="n">
-        <v>5.28681232075925</v>
-      </c>
-      <c r="L45" s="58" t="n">
-        <v>4.151802607324362</v>
-      </c>
-      <c r="M45" s="59" t="n">
-        <v>36.86862686176944</v>
-      </c>
-      <c r="N45" s="60" t="inlineStr">
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>€ 5.29 M</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="inlineStr">
+        <is>
+          <t>+€ 4.15 M</t>
+        </is>
+      </c>
+      <c r="M45" s="19" t="inlineStr">
+        <is>
+          <t>+€ 36.87 M</t>
+        </is>
+      </c>
+      <c r="N45" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="J46" s="53" t="n">
-        <v>14</v>
-      </c>
-      <c r="K46" s="54" t="n">
-        <v>5.336508356574386</v>
-      </c>
-      <c r="L46" s="54" t="n">
-        <v>4.191360651833212</v>
-      </c>
-      <c r="M46" s="55" t="n">
-        <v>41.05998751360265</v>
-      </c>
-      <c r="N46" s="56" t="inlineStr">
+      <c r="J46" s="29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K46" s="29" t="inlineStr">
+        <is>
+          <t>€ 5.34 M</t>
+        </is>
+      </c>
+      <c r="L46" s="29" t="inlineStr">
+        <is>
+          <t>+€ 4.19 M</t>
+        </is>
+      </c>
+      <c r="M46" s="30" t="inlineStr">
+        <is>
+          <t>+€ 41.06 M</t>
+        </is>
+      </c>
+      <c r="N46" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="J47" s="57" t="n">
-        <v>15</v>
-      </c>
-      <c r="K47" s="58" t="n">
-        <v>5.386671535126186</v>
-      </c>
-      <c r="L47" s="58" t="n">
-        <v>4.231290541960444</v>
-      </c>
-      <c r="M47" s="59" t="n">
-        <v>45.29127805556309</v>
-      </c>
-      <c r="N47" s="60" t="inlineStr">
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>€ 5.39 M</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="inlineStr">
+        <is>
+          <t>+€ 4.23 M</t>
+        </is>
+      </c>
+      <c r="M47" s="19" t="inlineStr">
+        <is>
+          <t>+€ 45.29 M</t>
+        </is>
+      </c>
+      <c r="N47" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
-      <c r="J48" s="53" t="n">
-        <v>16</v>
-      </c>
-      <c r="K48" s="54" t="n">
-        <v>5.437306247556372</v>
-      </c>
-      <c r="L48" s="54" t="n">
-        <v>4.271595773054873</v>
-      </c>
-      <c r="M48" s="55" t="n">
-        <v>49.56287382861797</v>
-      </c>
-      <c r="N48" s="56" t="inlineStr">
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K48" s="29" t="inlineStr">
+        <is>
+          <t>€ 5.44 M</t>
+        </is>
+      </c>
+      <c r="L48" s="29" t="inlineStr">
+        <is>
+          <t>+€ 4.27 M</t>
+        </is>
+      </c>
+      <c r="M48" s="30" t="inlineStr">
+        <is>
+          <t>+€ 49.56 M</t>
+        </is>
+      </c>
+      <c r="N48" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="J49" s="57" t="n">
-        <v>17</v>
-      </c>
-      <c r="K49" s="58" t="n">
-        <v>5.488416926283402</v>
-      </c>
-      <c r="L49" s="58" t="n">
-        <v>4.312279873321589</v>
-      </c>
-      <c r="M49" s="59" t="n">
-        <v>53.87515370193955</v>
-      </c>
-      <c r="N49" s="60" t="inlineStr">
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>€ 5.49 M</t>
+        </is>
+      </c>
+      <c r="L49" s="17" t="inlineStr">
+        <is>
+          <t>+€ 4.31 M</t>
+        </is>
+      </c>
+      <c r="M49" s="19" t="inlineStr">
+        <is>
+          <t>+€ 53.88 M</t>
+        </is>
+      </c>
+      <c r="N49" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="J50" s="53" t="n">
-        <v>18</v>
-      </c>
-      <c r="K50" s="54" t="n">
-        <v>5.540008045390466</v>
-      </c>
-      <c r="L50" s="54" t="n">
-        <v>4.353346404130811</v>
-      </c>
-      <c r="M50" s="55" t="n">
-        <v>58.22850010607037</v>
-      </c>
-      <c r="N50" s="56" t="inlineStr">
+      <c r="J50" s="29" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K50" s="29" t="inlineStr">
+        <is>
+          <t>€ 5.54 M</t>
+        </is>
+      </c>
+      <c r="L50" s="29" t="inlineStr">
+        <is>
+          <t>+€ 4.35 M</t>
+        </is>
+      </c>
+      <c r="M50" s="30" t="inlineStr">
+        <is>
+          <t>+€ 58.23 M</t>
+        </is>
+      </c>
+      <c r="N50" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="J51" s="57" t="n">
-        <v>19</v>
-      </c>
-      <c r="K51" s="58" t="n">
-        <v>5.592084121017137</v>
-      </c>
-      <c r="L51" s="58" t="n">
-        <v>4.39479896032964</v>
-      </c>
-      <c r="M51" s="59" t="n">
-        <v>62.62329906640001</v>
-      </c>
-      <c r="N51" s="60" t="inlineStr">
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
+        <is>
+          <t>€ 5.59 M</t>
+        </is>
+      </c>
+      <c r="L51" s="17" t="inlineStr">
+        <is>
+          <t>+€ 4.39 M</t>
+        </is>
+      </c>
+      <c r="M51" s="19" t="inlineStr">
+        <is>
+          <t>+€ 62.62 M</t>
+        </is>
+      </c>
+      <c r="N51" s="32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
-      <c r="J52" s="53" t="n">
-        <v>20</v>
-      </c>
-      <c r="K52" s="54" t="n">
-        <v>5.644649711754697</v>
-      </c>
-      <c r="L52" s="54" t="n">
-        <v>4.436641170556739</v>
-      </c>
-      <c r="M52" s="55" t="n">
-        <v>67.05994023695675</v>
-      </c>
-      <c r="N52" s="56" t="inlineStr">
+      <c r="J52" s="29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="inlineStr">
+        <is>
+          <t>€ 5.64 M</t>
+        </is>
+      </c>
+      <c r="L52" s="29" t="inlineStr">
+        <is>
+          <t>+€ 4.44 M</t>
+        </is>
+      </c>
+      <c r="M52" s="30" t="inlineStr">
+        <is>
+          <t>+€ 67.06 M</t>
+        </is>
+      </c>
+      <c r="N52" s="31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1994,58 +2230,33 @@
     <row r="53" ht="14" customHeight="1"/>
     <row r="54" ht="4" customHeight="1"/>
     <row r="55" ht="32" customHeight="1">
-      <c r="B55" s="65" t="inlineStr">
+      <c r="B55" s="35" t="inlineStr">
         <is>
           <t>Data sources: ENTSO-E Transparency Platform (FI day-ahead spot prices)  ·  Fingrid Open Data API: FCR-N (317), FCR-D up (318), FCR-D down (283), mFRR up (244), mFRR down (106)  ·  CAPEX benchmark: Ember Jan 2026  ·  IRR benchmark: 3–7% unlevered Western EU merchant BESS, Capstone DC Nov 2025  ·  Revenue benchmark: Exilion FI €40,700/MW/month H2 2023, Capalo AI Oct 2024  ·  Model note: SoC-optimised revenue assumes perfect price foresight; operational estimate applies −20% haircut for bidding friction and availability.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="B42:D42"/>
+  <mergeCells count="29">
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="E33:F33"/>
     <mergeCell ref="J10:K10"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="G36:H36"/>
     <mergeCell ref="B1:P1"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G37:H37"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E40:F40"/>
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B55:P55"/>
     <mergeCell ref="J13:P13"/>
     <mergeCell ref="B2:P3"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="G33:H33"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="N10:O10"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E36:F36"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
@@ -2053,16 +2264,8 @@
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="N9:O9"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="B13:H13"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="E37:F37"/>
     <mergeCell ref="J7:P7"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="B39:D39"/>
     <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
